--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620984.5528244195</v>
+        <v>620985</v>
       </c>
       <c r="R2" t="n">
-        <v>6726493.715136431</v>
+        <v>6726494</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>1998-07-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620984.5528244195</v>
+        <v>620985</v>
       </c>
       <c r="R3" t="n">
-        <v>6726493.715136431</v>
+        <v>6726494</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,19 +859,9 @@
           <t>1998-07-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1998-07-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,12 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -972,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620984.5528244195</v>
+        <v>620985</v>
       </c>
       <c r="R4" t="n">
-        <v>6726493.715136431</v>
+        <v>6726494</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1005,19 +970,9 @@
           <t>1998-07-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1998-07-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>98601</v>
+        <v>98607</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>98602</v>
+        <v>98608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>98607</v>
+        <v>98610</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>98608</v>
+        <v>98611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>98610</v>
+        <v>98613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>98613</v>
+        <v>98614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>98614</v>
+        <v>98641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>98641</v>
+        <v>98647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>98642</v>
+        <v>98648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>98647</v>
+        <v>98654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>98648</v>
+        <v>98655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>98654</v>
+        <v>98658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>98655</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>98658</v>
+        <v>98665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>98668</v>
+        <v>98673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99182329</v>
       </c>
       <c r="B2" t="n">
-        <v>98673</v>
+        <v>98681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>99182324</v>
       </c>
       <c r="B3" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>99182319</v>
       </c>
       <c r="B4" t="n">
-        <v>98674</v>
+        <v>98682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99182329</v>
+        <v>99182284</v>
       </c>
       <c r="B2" t="n">
-        <v>98681</v>
+        <v>111390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björsjön, västsidan, ovan fd inägor, Gstr</t>
+          <t>Björsjön, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620985</v>
+        <v>621035</v>
       </c>
       <c r="R2" t="n">
-        <v>6726494</v>
+        <v>6726467</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,11 +748,6 @@
           <t>1998-07-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3 ex av nästrot, här i tät örtvegetation + 3 ex i översluten barryta</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>skog, Blandskog, 80-årig barrdominerad skog i utströmningsområde lundartad örtflora helt utan ris, mullrik morän.</t>
+          <t>skog, Granskog, m tall-o lövinslag, ängsgranskog i moränsluttn utströmn.omr mot strand, mullrik, föga blockig moränmark. 80-100 årig hög gles skog. Rik flora med nästrot, sårläka och tibast mfl</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 176685N</t>
+          <t>Gst Fyndnr 176730L</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99182324</v>
+        <v>102027044</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +797,57 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björsjön, västsidan, ovan fd inägor, Gstr</t>
+          <t>Vägkant, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620985</v>
+        <v>620912</v>
       </c>
       <c r="R3" t="n">
-        <v>6726494</v>
+        <v>6726180</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1998-07-03</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1998-07-03</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,42 +885,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>skog, Blandskog, 80-årig barrdominerad skog i utströmningsområde lundartad örtflora helt utan ris, mullrik morän.</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 176690N</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Evelina Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Gästriklands flora (2016)</t>
-        </is>
-      </c>
+          <t>Evelina Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99182319</v>
+        <v>102027316</v>
       </c>
       <c r="B4" t="n">
-        <v>98682</v>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,34 +915,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björsjön, västsidan, ovan fd inägor, Gstr</t>
+          <t>skog, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620985</v>
+        <v>620949</v>
       </c>
       <c r="R4" t="n">
-        <v>6726494</v>
+        <v>6726159</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -967,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1998-07-03</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1998-07-03</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,47 +999,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>skog, Blandskog, 80-årig barrdominerad skog i utströmningsområde lundartad örtflora helt utan ris, mullrik morän.</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 176695N</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Evelina Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Gästriklands flora (2016)</t>
-        </is>
-      </c>
+          <t>Evelina Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102027694</v>
+        <v>102027337</v>
       </c>
       <c r="B5" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620996.0157690113</v>
+        <v>620996</v>
       </c>
       <c r="R5" t="n">
-        <v>6726197.226853794</v>
+        <v>6726197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,19 +1106,9 @@
           <t>2022-07-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,15 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102027316</v>
+        <v>102027410</v>
       </c>
       <c r="B6" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,24 +1176,28 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>skog, Gstr</t>
+          <t>Skogen, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620949.6472562292</v>
+        <v>620946</v>
       </c>
       <c r="R6" t="n">
-        <v>6726158.370019282</v>
+        <v>6726193</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,19 +1224,9 @@
           <t>2022-07-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,15 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102027044</v>
+        <v>99182298</v>
       </c>
       <c r="B7" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,57 +1265,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vägkant, Gstr</t>
+          <t>Björsjön, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620912.5403183139</v>
+        <v>621035</v>
       </c>
       <c r="R7" t="n">
-        <v>6726180.18467745</v>
+        <v>6726467</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,22 +1319,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-02</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-07-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-07-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,34 +1333,42 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>skog, Granskog, m tall-o lövinslag, ängsgranskog i moränsluttn utströmn.omr mot strand, mullrik, föga blockig moränmark. 80-100 årig hög gles skog. Rik flora med nästrot, sårläka och tibast mfl</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 176716L</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Evelina Persson</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Evelina Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102027410</v>
+        <v>99182319</v>
       </c>
       <c r="B8" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,57 +1376,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skogen, Gstr</t>
+          <t>Björsjön, västsidan, ovan fd inägor, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620946.0039746796</v>
+        <v>620985</v>
       </c>
       <c r="R8" t="n">
-        <v>6726193.579469733</v>
+        <v>6726494</v>
       </c>
       <c r="S8" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,22 +1430,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-07-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-07-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,22 +1444,706 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>skog, Blandskog, 80-årig barrdominerad skog i utströmningsområde lundartad örtflora helt utan ris, mullrik morän.</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 176695N</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Evelina Persson</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Evelina Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>99182294</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björsjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>621035</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6726467</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>skog, Granskog, m tall-o lövinslag, ängsgranskog i moränsluttn utströmn.omr mot strand, mullrik, föga blockig moränmark. 80-100 årig hög gles skog. Rik flora med nästrot, sårläka och tibast mfl</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 176720L</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>99182329</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björsjön, västsidan, ovan fd inägor, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>620985</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6726494</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3 ex av nästrot, här i tät örtvegetation + 3 ex i översluten barryta</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>skog, Blandskog, 80-årig barrdominerad skog i utströmningsområde lundartad örtflora helt utan ris, mullrik morän.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 176685N</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>99182289</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björsjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>621035</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6726467</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>skog, Granskog, m tall-o lövinslag, ängsgranskog i moränsluttn utströmn.omr mot strand, mullrik, föga blockig moränmark. 80-100 årig hög gles skog. Rik flora med nästrot, sårläka och tibast mfl</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 176725L</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>99182308</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björsjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>621035</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6726467</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>skog, Granskog, m tall-o lövinslag, ängsgranskog i moränsluttn utströmn.omr mot strand, mullrik, föga blockig moränmark. 80-100 årig hög gles skog. Rik flora med nästrot, sårläka och tibast mfl</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 176706L</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>99182301</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björsjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>621035</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6726467</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>skog, Granskog, m tall-o lövinslag, ängsgranskog i moränsluttn utströmn.omr mot strand, mullrik, föga blockig moränmark. 80-100 årig hög gles skog. Rik flora med nästrot, sårläka och tibast mfl</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 176713L</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>99182324</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björsjön, västsidan, ovan fd inägor, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>620985</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6726494</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1998-07-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>skog, Blandskog, 80-årig barrdominerad skog i utströmningsområde lundartad örtflora helt utan ris, mullrik morän.</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 176690N</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33904-2025 artfynd.xlsx
+++ b/artfynd/A 33904-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99182284</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102027044</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102027316</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102027337</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1251,6 +1276,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102027410</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99182298</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1473,6 +1508,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99182319</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99182294</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1700,6 +1745,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99182329</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1811,6 +1861,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99182289</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1922,6 +1977,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99182308</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2033,6 +2093,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99182301</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2144,8 +2209,28 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99182324</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>